--- a/data/trans_dic/P3A$personadelacasa-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Provincia-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>25,85; 41,63</t>
+          <t>26,26; 41,44</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,23; 34,2</t>
+          <t>24,31; 34,57</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,7; 35,51</t>
+          <t>26,55; 35,92</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>27,52; 39,59</t>
+          <t>28,4; 40,75</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>22,71; 30,43</t>
+          <t>23,1; 30,4</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,81; 34,28</t>
+          <t>26,58; 33,87</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,58; 31,31</t>
+          <t>20,53; 31,47</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,5; 27,16</t>
+          <t>18,72; 27,49</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,69; 27,53</t>
+          <t>20,93; 27,72</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,57; 25,83</t>
+          <t>11,84; 26,64</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6,59; 18,31</t>
+          <t>7,49; 18,24</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,21; 19,72</t>
+          <t>10,42; 19,61</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,35; 49,35</t>
+          <t>36,94; 49,69</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,86; 76,41</t>
+          <t>45,59; 76,66</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>44,17; 67,95</t>
+          <t>43,67; 67,31</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>16,76; 26,94</t>
+          <t>17,44; 27,42</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,94; 30,0</t>
+          <t>19,64; 29,99</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,81; 26,88</t>
+          <t>19,65; 27,02</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,69; 34,36</t>
+          <t>24,68; 33,81</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>10,94; 28,76</t>
+          <t>9,64; 29,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>14,94; 29,56</t>
+          <t>15,68; 29,68</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,2; 26,59</t>
+          <t>8,46; 26,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,88; 24,56</t>
+          <t>18,87; 24,69</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>11,87; 24,41</t>
+          <t>12,87; 24,29</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,98; 29,13</t>
+          <t>20,6; 28,95</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>20,53; 27,76</t>
+          <t>19,87; 27,64</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,23; 27,51</t>
+          <t>22,48; 27,55</t>
         </is>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Hogares en los que al menos otra persona se ocupa principalmente de las tareas domésticas</t>
+          <t>Hogares en los que, al menos, principalmente otra persona del hogar se ocupa de las tareas domésticas (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>80520; 129656</t>
+          <t>81788; 129050</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70171; 99044</t>
+          <t>70397; 100119</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>160486; 213419</t>
+          <t>159578; 215935</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>142673; 205213</t>
+          <t>147234; 211224</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>116933; 156709</t>
+          <t>118983; 156562</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>277000; 354200</t>
+          <t>274645; 349972</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64926; 98753</t>
+          <t>64749; 99246</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>64372; 94495</t>
+          <t>65109; 95629</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>137251; 182610</t>
+          <t>138835; 183856</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>36165; 80747</t>
+          <t>37020; 83261</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>31361; 87093</t>
+          <t>35654; 86773</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>80516; 155425</t>
+          <t>82176; 154572</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>64798; 87986</t>
+          <t>65850; 88581</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>118675; 197733</t>
+          <t>117977; 198378</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>193050; 296985</t>
+          <t>190882; 294198</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>45200; 72643</t>
+          <t>47033; 73928</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>51258; 77113</t>
+          <t>50476; 77098</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>104362; 141564</t>
+          <t>103473; 142292</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154157; 214518</t>
+          <t>154058; 211070</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>92935; 244265</t>
+          <t>81893; 246534</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>220196; 435562</t>
+          <t>231125; 437383</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>76197; 246981</t>
+          <t>78528; 249702</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>135491; 176302</t>
+          <t>135439; 177184</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>195445; 401831</t>
+          <t>211883; 399892</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>725812; 1007587</t>
+          <t>712530; 1001359</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>761999; 1030299</t>
+          <t>737230; 1025692</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1593901; 1972494</t>
+          <t>1611652; 1974983</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P3A$personadelacasa-Provincia-trans_dic.xlsx
+++ b/data/trans_dic/P3A$personadelacasa-Provincia-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>33,16%</t>
+          <t>30,9%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>31,02%</t>
+          <t>30,46%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>26,26; 41,44</t>
+          <t>25,25; 36,48</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>24,31; 34,57</t>
+          <t>25,87; 35,54</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>26,55; 35,92</t>
+          <t>26,74; 34,18</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>33,78%</t>
+          <t>32,0%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>26,44%</t>
+          <t>26,51%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>30,12%</t>
+          <t>29,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>28,4; 40,75</t>
+          <t>26,34; 37,9</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>23,1; 30,4</t>
+          <t>22,64; 30,37</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>26,58; 33,87</t>
+          <t>25,84; 32,55</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>25,12%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>22,79%</t>
+          <t>22,51%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>24,18%</t>
+          <t>23,74%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>20,53; 31,47</t>
+          <t>20,28; 30,95</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>18,72; 27,49</t>
+          <t>18,51; 27,05</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>20,93; 27,72</t>
+          <t>20,69; 27,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,0%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>14,68%</t>
+          <t>16,66%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>11,84; 26,64</t>
+          <t>11,43; 23,94</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7,49; 18,24</t>
+          <t>12,25; 21,78</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>10,42; 19,61</t>
+          <t>13,12; 20,5</t>
         </is>
       </c>
     </row>
@@ -749,17 +749,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>43,26%</t>
+          <t>42,6%</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>57,14%</t>
+          <t>47,16%</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>51,48%</t>
+          <t>45,0%</t>
         </is>
       </c>
     </row>
@@ -772,17 +772,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>36,94; 49,69</t>
+          <t>36,72; 48,42</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>45,59; 76,66</t>
+          <t>42,38; 51,94</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>43,67; 67,31</t>
+          <t>40,95; 48,64</t>
         </is>
       </c>
     </row>
@@ -799,17 +799,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>22,07%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,92%</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23,24%</t>
+          <t>22,49%</t>
         </is>
       </c>
     </row>
@@ -822,17 +822,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17,44; 27,42</t>
+          <t>16,63; 26,0</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>19,64; 29,99</t>
+          <t>19,7; 28,91</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>19,65; 27,02</t>
+          <t>19,13; 25,73</t>
         </is>
       </c>
     </row>
@@ -849,17 +849,17 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>29,16%</t>
+          <t>28,98%</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>21,02%</t>
+          <t>27,14%</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>24,47%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -872,17 +872,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,68; 33,81</t>
+          <t>25,09; 33,91</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,64; 29,03</t>
+          <t>24,09; 30,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,68; 29,68</t>
+          <t>25,21; 31,06</t>
         </is>
       </c>
     </row>
@@ -899,17 +899,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>26,32%</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,6%</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20,14%</t>
+          <t>23,91%</t>
         </is>
       </c>
     </row>
@@ -922,17 +922,17 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>8,46; 26,89</t>
+          <t>22,54; 30,36</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>18,87; 24,69</t>
+          <t>18,85; 24,52</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>12,87; 24,29</t>
+          <t>21,73; 26,24</t>
         </is>
       </c>
     </row>
@@ -949,17 +949,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>26,32%</t>
+          <t>27,58%</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>26,46%</t>
         </is>
       </c>
     </row>
@@ -972,17 +972,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>20,6; 28,95</t>
+          <t>25,8; 29,57</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>19,87; 27,64</t>
+          <t>24,02; 26,9</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>22,48; 27,55</t>
+          <t>25,24; 27,66</t>
         </is>
       </c>
     </row>
@@ -1111,17 +1111,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>103270</t>
+          <t>98533</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>83200</t>
+          <t>94880</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>186470</t>
+          <t>193412</t>
         </is>
       </c>
     </row>
@@ -1134,17 +1134,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>81788; 129050</t>
+          <t>80495; 116325</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>70397; 100119</t>
+          <t>81763; 112319</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>159578; 215935</t>
+          <t>169791; 217033</t>
         </is>
       </c>
     </row>
@@ -1184,17 +1184,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>175138</t>
+          <t>169824</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>136140</t>
+          <t>144899</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>311278</t>
+          <t>314723</t>
         </is>
       </c>
     </row>
@@ -1207,17 +1207,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>147234; 211224</t>
+          <t>139760; 201114</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>118983; 156562</t>
+          <t>123715; 165966</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>274645; 349972</t>
+          <t>278286; 350597</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>81088</t>
+          <t>79227</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>79295</t>
+          <t>79930</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160383</t>
+          <t>159156</t>
         </is>
       </c>
     </row>
@@ -1280,17 +1280,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>64749; 99246</t>
+          <t>63964; 97596</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>65109; 95629</t>
+          <t>65722; 96047</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>138835; 183856</t>
+          <t>138743; 182681</t>
         </is>
       </c>
     </row>
@@ -1330,17 +1330,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>54911</t>
+          <t>63417</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>60845</t>
+          <t>69082</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115756</t>
+          <t>132499</t>
         </is>
       </c>
     </row>
@@ -1353,17 +1353,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>37020; 83261</t>
+          <t>42659; 89345</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35654; 86773</t>
+          <t>51696; 91915</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>82176; 154572</t>
+          <t>104329; 162964</t>
         </is>
       </c>
     </row>
@@ -1403,17 +1403,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>77115</t>
+          <t>87405</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>147866</t>
+          <t>107953</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>224982</t>
+          <t>195358</t>
         </is>
       </c>
     </row>
@@ -1426,17 +1426,17 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>65850; 88581</t>
+          <t>75346; 99355</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>117977; 198378</t>
+          <t>97022; 118902</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>190882; 294198</t>
+          <t>177772; 211159</t>
         </is>
       </c>
     </row>
@@ -1476,17 +1476,17 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>59519</t>
+          <t>57104</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>62884</t>
+          <t>63077</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>122403</t>
+          <t>120182</t>
         </is>
       </c>
     </row>
@@ -1499,17 +1499,17 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>47033; 73928</t>
+          <t>45028; 70373</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>50476; 77098</t>
+          <t>51949; 76242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>103473; 142292</t>
+          <t>102253; 137527</t>
         </is>
       </c>
     </row>
@@ -1549,17 +1549,17 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>182013</t>
+          <t>208562</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>178513</t>
+          <t>209568</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>360526</t>
+          <t>418130</t>
         </is>
       </c>
     </row>
@@ -1572,17 +1572,17 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>154058; 211070</t>
+          <t>180544; 244062</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>81893; 246534</t>
+          <t>186008; 238492</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>231125; 437383</t>
+          <t>376033; 463396</t>
         </is>
       </c>
     </row>
@@ -1622,17 +1622,17 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
-          <t>177305</t>
+          <t>210061</t>
         </is>
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>154314</t>
+          <t>179534</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>331619</t>
+          <t>389595</t>
         </is>
       </c>
     </row>
@@ -1645,17 +1645,17 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>78528; 249702</t>
+          <t>179885; 242259</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>135439; 177184</t>
+          <t>156692; 203843</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>211883; 399892</t>
+          <t>354096; 427576</t>
         </is>
       </c>
     </row>
@@ -1695,17 +1695,17 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>910358</t>
+          <t>974134</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>903057</t>
+          <t>948922</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1813415</t>
+          <t>1923057</t>
         </is>
       </c>
     </row>
@@ -1718,17 +1718,17 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
-          <t>712530; 1001359</t>
+          <t>911085; 1044348</t>
         </is>
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>737230; 1025692</t>
+          <t>897206; 1004927</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>1611652; 1974983</t>
+          <t>1834414; 2009994</t>
         </is>
       </c>
     </row>
